--- a/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,0</t>
+          <t>-3,23; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 3,11</t>
+          <t>-1,87; 2,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,18</t>
+          <t>-3,19; 3,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,0</t>
+          <t>-4,53; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,83</t>
+          <t>-3,86; 0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,0</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,39</t>
+          <t>-2,54; 3,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,77</t>
+          <t>0,71; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,2; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,42</t>
+          <t>-0,67; 1,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,1</t>
+          <t>-0,38; 0,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,16</t>
+          <t>-0,1; 2,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-78,95; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-52,24; —</t>
+          <t>-51,27; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,0</t>
+          <t>-3,25; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,95</t>
+          <t>-1,86; 3,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,1</t>
+          <t>-3,34; 3,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,0</t>
+          <t>-4,88; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,81</t>
+          <t>-4,1; 0,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,0</t>
+          <t>-3,83; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 3,46</t>
+          <t>-2,79; 3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,56</t>
+          <t>0,79; 6,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,0</t>
+          <t>-1,25; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,51</t>
+          <t>-0,75; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,97</t>
+          <t>-0,38; 0,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,18</t>
+          <t>-0,14; 2,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,1; 749,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,27; —</t>
+          <t>-67,49; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,0</t>
+          <t>-3,26; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -670,12 +670,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>259,65%</t>
         </is>
       </c>
     </row>
@@ -765,17 +765,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 3,0</t>
+          <t>-0,28; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-54,64%</t>
+          <t>-58,42%</t>
         </is>
       </c>
     </row>
@@ -865,17 +865,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 3,07</t>
+          <t>-3,19; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,0</t>
+          <t>-4,52; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,79</t>
+          <t>-3,53; 0,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,0</t>
+          <t>-3,87; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,56</t>
+          <t>-2,58; 3,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,96</t>
+          <t>0,77; 6,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>199,63%</t>
+          <t>312,44%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,0</t>
+          <t>-1,12; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,44</t>
+          <t>-0,69; 1,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,94</t>
+          <t>-0,38; 1,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,24</t>
+          <t>0,18; 2,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 749,61</t>
+          <t>-78,95; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-67,49; —</t>
+          <t>-35,58; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C06-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,44 +619,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-0,64</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
+      <c r="C4" s="5" t="n">
+        <v>-0.6383906177879889</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.088574132514261</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.080722598212708</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -655,254 +650,132 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,26; 0,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,01</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,09</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.259247767748215</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>7.009259688572691</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.086626289301568</v>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,58</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>259,65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,93</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,43</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-0,28; 3,76</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5168706682942327</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5758136982344552</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.024808906138278</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>2.596507021198549</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,91</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,89%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-58,42%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr"/>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-0.2759311355253411</v>
+      </c>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-3,19; 3,18</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,52; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,53; 0,74</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr"/>
+      <c r="D9" s="5" t="n">
+        <v>2.92666913843274</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.426236714680887</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.764597488503605</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +783,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,79</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.4395955312290596</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9103020491816716</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.5025003668450153</v>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="n">
+        <v>0.4088750675029086</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.5841712692613167</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,87; 0,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,58; 3,39</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,77; 6,63</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>-3.190600710022024</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.520692760436754</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.534475595825302</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>3.175659435685203</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.7355135551567445</v>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.7715632008523419</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.2164493767888276</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.787372823638343</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1526784980750211</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-3.872576911101359</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.575015562928523</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>0.7653624485727804</v>
+      </c>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3.390264441143461</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>6.634591016473013</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,09</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>50,24%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>101,37%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>312,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,12; 0,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-0,69; 1,42</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,38; 1,1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 2,31</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-78,95; —</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-35,58; —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.3371073952524881</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.3051030002897893</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1927332801654046</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.087512944899093</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.5024020095113768</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>1.013700005267459</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>3.124353784430062</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.123793041034699</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6873021635972862</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.3795172282345824</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.1764436343200297</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="n">
+        <v>-0.7894870454470079</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="6" t="n">
+        <v>-0.3558490405840401</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.416790844001865</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.101722491133976</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.309662755907967</v>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr"/>
+      <c r="J18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1027,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
